--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D895B834-87E3-478C-8070-3641B71D7FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD8BFED-682B-433E-B028-222A732D1228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="3285" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3630" yWindow="3630" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1245"/>
+  <dimension ref="A1:D1246"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17795,6 +17795,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1246" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1246" s="1">
+        <v>46278</v>
+      </c>
+      <c r="B1246" s="2">
+        <v>0.44050925925925927</v>
+      </c>
+      <c r="C1246">
+        <v>179702</v>
+      </c>
+      <c r="D1246">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BD8BFED-682B-433E-B028-222A732D1228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04F52C4-7A6D-450F-8A88-A5AE646DA4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="3630" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3975" yWindow="3975" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1246"/>
+  <dimension ref="A1:D1247"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17809,6 +17809,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1247" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1247" s="1">
+        <v>46279</v>
+      </c>
+      <c r="B1247" s="2">
+        <v>0.68364583333333329</v>
+      </c>
+      <c r="C1247">
+        <v>179710</v>
+      </c>
+      <c r="D1247">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04F52C4-7A6D-450F-8A88-A5AE646DA4CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631560A9-7808-49A1-9305-DB0F0A827582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="3975" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="4320" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1247"/>
+  <dimension ref="A1:D1248"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17823,6 +17823,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1248" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1248" s="1">
+        <v>46280</v>
+      </c>
+      <c r="B1248" s="2">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="C1248">
+        <v>179825</v>
+      </c>
+      <c r="D1248">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{631560A9-7808-49A1-9305-DB0F0A827582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A507FA-8721-41C1-9AA3-1A1AE6C668F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="4320" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4665" yWindow="4665" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1248"/>
+  <dimension ref="A1:D1249"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17837,6 +17837,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1249" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1249" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B1249" s="2">
+        <v>0.63928240740740738</v>
+      </c>
+      <c r="C1249">
+        <v>179802</v>
+      </c>
+      <c r="D1249">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3A507FA-8721-41C1-9AA3-1A1AE6C668F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152833F6-E34B-46A0-83AD-71904DFF6036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4665" yWindow="4665" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5010" yWindow="5010" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1249"/>
+  <dimension ref="A1:D1250"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17851,6 +17851,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1250" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1250" s="1">
+        <v>46282</v>
+      </c>
+      <c r="B1250" s="2">
+        <v>0.64908564814814818</v>
+      </c>
+      <c r="C1250">
+        <v>179864</v>
+      </c>
+      <c r="D1250">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{152833F6-E34B-46A0-83AD-71904DFF6036}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2283DA-775A-40CF-84E5-C9D23AB89BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5010" yWindow="5010" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5355" yWindow="5355" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1250"/>
+  <dimension ref="A1:D1251"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17865,6 +17865,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1251" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1251" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B1251" s="2">
+        <v>0.67166666666666663</v>
+      </c>
+      <c r="C1251">
+        <v>179876</v>
+      </c>
+      <c r="D1251">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2283DA-775A-40CF-84E5-C9D23AB89BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A22ACF-95E5-446D-A563-33BA790E4255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5355" yWindow="5355" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5700" yWindow="5700" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1251"/>
+  <dimension ref="A1:D1252"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17879,6 +17879,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1252" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1252" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B1252" s="2">
+        <v>0.48427083333333332</v>
+      </c>
+      <c r="C1252">
+        <v>179905</v>
+      </c>
+      <c r="D1252">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A22ACF-95E5-446D-A563-33BA790E4255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B32C62-A6AF-4F45-8F9F-3378CD7C19D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5700" yWindow="5700" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6045" yWindow="6045" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1252"/>
+  <dimension ref="A1:D1253"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17893,6 +17893,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1253" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1253" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B1253" s="2">
+        <v>0.4291550925925926</v>
+      </c>
+      <c r="C1253">
+        <v>179907</v>
+      </c>
+      <c r="D1253">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4B32C62-A6AF-4F45-8F9F-3378CD7C19D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEC9792-0200-4EF7-9AE7-450FB6D67DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6045" yWindow="6045" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1253"/>
+  <dimension ref="A1:D1254"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17907,6 +17907,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1254" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1254" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B1254" s="2">
+        <v>0.38440972222222225</v>
+      </c>
+      <c r="C1254">
+        <v>179907</v>
+      </c>
+      <c r="D1254">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAEC9792-0200-4EF7-9AE7-450FB6D67DBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB847E0-BEA5-44BC-A937-E7D396C4DE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1254"/>
+  <dimension ref="A1:D1255"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17921,6 +17921,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1255" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1255" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B1255" s="2">
+        <v>0.47414351851851849</v>
+      </c>
+      <c r="C1255">
+        <v>179944</v>
+      </c>
+      <c r="D1255">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB847E0-BEA5-44BC-A937-E7D396C4DE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1722397F-26C8-4A86-97C4-64E043790FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1515" yWindow="1515" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1255"/>
+  <dimension ref="A1:D1256"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17935,6 +17935,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1256" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1256" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B1256" s="2">
+        <v>0.43328703703703703</v>
+      </c>
+      <c r="C1256">
+        <v>179953</v>
+      </c>
+      <c r="D1256">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1722397F-26C8-4A86-97C4-64E043790FCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344F729B-DA80-475B-8DA4-CE861A6468A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1256"/>
+  <dimension ref="A1:D1257"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17949,6 +17949,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1257" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1257" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B1257" s="2">
+        <v>0.44284722222222223</v>
+      </c>
+      <c r="C1257">
+        <v>179961</v>
+      </c>
+      <c r="D1257">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344F729B-DA80-475B-8DA4-CE861A6468A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E0206E-65D1-48C9-AB91-6522FD238708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1860" yWindow="1860" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1257"/>
+  <dimension ref="A1:D1258"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17963,6 +17963,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1258" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1258" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B1258" s="2">
+        <v>0.4450810185185185</v>
+      </c>
+      <c r="C1258">
+        <v>179953</v>
+      </c>
+      <c r="D1258">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94E0206E-65D1-48C9-AB91-6522FD238708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DC4DCC-48EF-46D9-B865-EF88DB57C37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2550" yWindow="2550" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1258"/>
+  <dimension ref="A1:D1259"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17977,6 +17977,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1259" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1259" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B1259" s="2">
+        <v>0.47559027777777779</v>
+      </c>
+      <c r="C1259">
+        <v>179984</v>
+      </c>
+      <c r="D1259">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16DC4DCC-48EF-46D9-B865-EF88DB57C37B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C2A559-8D97-4B89-B6C9-03344B403433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2550" yWindow="2550" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2895" yWindow="2895" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1259"/>
+  <dimension ref="A1:D1260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -17991,6 +17991,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1260" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1260" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B1260" s="2">
+        <v>0.48275462962962962</v>
+      </c>
+      <c r="C1260">
+        <v>179998</v>
+      </c>
+      <c r="D1260">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26C2A559-8D97-4B89-B6C9-03344B403433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8403DF-13C4-4074-82A6-6A311CC4F8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2895" yWindow="2895" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3240" yWindow="3240" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1260"/>
+  <dimension ref="A1:D1261"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18005,6 +18005,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1261" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1261" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B1261" s="2">
+        <v>0.6457060185185185</v>
+      </c>
+      <c r="C1261">
+        <v>180065</v>
+      </c>
+      <c r="D1261">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8403DF-13C4-4074-82A6-6A311CC4F8EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A6BF3E-01A8-4C54-99F4-726DF9D15253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3240" yWindow="3240" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1261"/>
+  <dimension ref="A1:D1262"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18019,6 +18019,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1262" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1262" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B1262" s="2">
+        <v>0.63320601851851854</v>
+      </c>
+      <c r="C1262">
+        <v>180158</v>
+      </c>
+      <c r="D1262">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A6BF3E-01A8-4C54-99F4-726DF9D15253}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0E176A-B05C-49D0-80D7-2B406E612B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="3240" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3585" yWindow="3585" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1262"/>
+  <dimension ref="A1:D1263"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18033,6 +18033,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1263" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1263" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B1263" s="2">
+        <v>0.6704282407407407</v>
+      </c>
+      <c r="C1263">
+        <v>180196</v>
+      </c>
+      <c r="D1263">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D0E176A-B05C-49D0-80D7-2B406E612B69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AFCDF6-AF42-4356-B80B-E6B0A1424CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3585" yWindow="3585" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3930" yWindow="3930" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1263"/>
+  <dimension ref="A1:D1264"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18047,6 +18047,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1264" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1264" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B1264" s="2">
+        <v>0.65238425925925925</v>
+      </c>
+      <c r="C1264">
+        <v>180292</v>
+      </c>
+      <c r="D1264">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93AFCDF6-AF42-4356-B80B-E6B0A1424CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1F7E9E-CD62-477D-A30D-79E169204DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3930" yWindow="3930" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4275" yWindow="4275" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1264"/>
+  <dimension ref="A1:D1265"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18061,6 +18061,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1265" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1265" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B1265" s="2">
+        <v>0.63594907407407408</v>
+      </c>
+      <c r="C1265">
+        <v>180333</v>
+      </c>
+      <c r="D1265">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE1F7E9E-CD62-477D-A30D-79E169204DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD9F01-F168-42FB-B1E1-2CEE895EF35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4275" yWindow="4275" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4620" yWindow="4620" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1265"/>
+  <dimension ref="A1:D1266"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18075,6 +18075,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1266" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1266" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B1266" s="2">
+        <v>0.39951388888888889</v>
+      </c>
+      <c r="C1266">
+        <v>180347</v>
+      </c>
+      <c r="D1266">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BD9F01-F168-42FB-B1E1-2CEE895EF35D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98ACA6E-DDF7-4645-B1BF-9F5063138761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="4620" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4965" yWindow="4965" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1266"/>
+  <dimension ref="A1:D1267"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18089,6 +18089,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1267" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1267" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B1267" s="2">
+        <v>0.4654861111111111</v>
+      </c>
+      <c r="C1267">
+        <v>180347</v>
+      </c>
+      <c r="D1267">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D98ACA6E-DDF7-4645-B1BF-9F5063138761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C2D50B-CE79-43F6-8DEB-03DCD94E53CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4965" yWindow="4965" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5310" yWindow="5310" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1267"/>
+  <dimension ref="A1:D1268"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18103,6 +18103,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1268" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1268" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B1268" s="2">
+        <v>0.6372106481481481</v>
+      </c>
+      <c r="C1268">
+        <v>180352</v>
+      </c>
+      <c r="D1268">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C2D50B-CE79-43F6-8DEB-03DCD94E53CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9A2F98-85DC-4DE3-AC48-94630BCCBF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5310" yWindow="5310" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5655" yWindow="5655" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1268"/>
+  <dimension ref="A1:D1269"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18117,6 +18117,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1269" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1269" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B1269" s="2">
+        <v>0.6325925925925926</v>
+      </c>
+      <c r="C1269">
+        <v>180397</v>
+      </c>
+      <c r="D1269">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9A2F98-85DC-4DE3-AC48-94630BCCBF7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC0AFF3-BDD8-4317-BB3B-7A6B89FAA1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5655" yWindow="5655" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6000" yWindow="6000" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1269"/>
+  <dimension ref="A1:D1270"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18131,6 +18131,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1270" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1270" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B1270" s="2">
+        <v>0.63325231481481481</v>
+      </c>
+      <c r="C1270">
+        <v>180710</v>
+      </c>
+      <c r="D1270">
+        <v>6860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDC0AFF3-BDD8-4317-BB3B-7A6B89FAA1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D74324C-A5F0-4642-94D9-957CCF632955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="6000" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1270"/>
+  <dimension ref="A1:D1271"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18145,6 +18145,20 @@
         <v>6860</v>
       </c>
     </row>
+    <row r="1271" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1271" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B1271" s="2">
+        <v>0.6355439814814815</v>
+      </c>
+      <c r="C1271">
+        <v>180715</v>
+      </c>
+      <c r="D1271">
+        <v>6860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D74324C-A5F0-4642-94D9-957CCF632955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E6C14C-B700-4279-9F12-0269668543E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2685" yWindow="2685" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1271"/>
+  <dimension ref="A1:D1272"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18159,6 +18159,20 @@
         <v>6860</v>
       </c>
     </row>
+    <row r="1272" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1272" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B1272" s="2">
+        <v>0.64077546296296295</v>
+      </c>
+      <c r="C1272">
+        <v>180742</v>
+      </c>
+      <c r="D1272">
+        <v>6860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E6C14C-B700-4279-9F12-0269668543E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B68AB9-8455-48DB-8009-D5DBB7846353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2685" yWindow="2685" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3030" yWindow="3030" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1272"/>
+  <dimension ref="A1:D1273"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18173,6 +18173,20 @@
         <v>6860</v>
       </c>
     </row>
+    <row r="1273" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1273" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B1273" s="2">
+        <v>0.3913773148148148</v>
+      </c>
+      <c r="C1273">
+        <v>180885</v>
+      </c>
+      <c r="D1273">
+        <v>6860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81B68AB9-8455-48DB-8009-D5DBB7846353}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641C003E-A1B2-4416-AE9C-BE0D52FA12CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="3030" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3375" yWindow="3375" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1273"/>
+  <dimension ref="A1:D1274"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18187,6 +18187,20 @@
         <v>6860</v>
       </c>
     </row>
+    <row r="1274" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1274" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B1274" s="2">
+        <v>0.44524305555555554</v>
+      </c>
+      <c r="C1274">
+        <v>180887</v>
+      </c>
+      <c r="D1274">
+        <v>6860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{641C003E-A1B2-4416-AE9C-BE0D52FA12CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F672D0-A12F-45B0-BA61-FEEC60E3DB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3375" yWindow="3375" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="3720" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1274"/>
+  <dimension ref="A1:D1275"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18201,6 +18201,20 @@
         <v>6860</v>
       </c>
     </row>
+    <row r="1275" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1275" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B1275" s="2">
+        <v>0.63581018518518517</v>
+      </c>
+      <c r="C1275">
+        <v>180903</v>
+      </c>
+      <c r="D1275">
+        <v>6860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F672D0-A12F-45B0-BA61-FEEC60E3DB0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F1E55C-EF26-4B59-9862-A4FB96DCAA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3720" yWindow="3720" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1275"/>
+  <dimension ref="A1:D1276"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18215,6 +18215,20 @@
         <v>6860</v>
       </c>
     </row>
+    <row r="1276" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1276" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B1276" s="2">
+        <v>0.62927083333333333</v>
+      </c>
+      <c r="C1276">
+        <v>180919</v>
+      </c>
+      <c r="D1276">
+        <v>6860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48F1E55C-EF26-4B59-9862-A4FB96DCAA81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69061854-54F2-4BCA-9463-4BD0C5AF175A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="3720" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4065" yWindow="4065" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1276"/>
+  <dimension ref="A1:D1277"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18229,6 +18229,20 @@
         <v>6860</v>
       </c>
     </row>
+    <row r="1277" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1277" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B1277" s="2">
+        <v>0.62799768518518517</v>
+      </c>
+      <c r="C1277">
+        <v>180949</v>
+      </c>
+      <c r="D1277">
+        <v>6860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69061854-54F2-4BCA-9463-4BD0C5AF175A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A79A27-4F72-4748-824A-5D3A95FC4355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4065" yWindow="4065" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1277"/>
+  <dimension ref="A1:D1278"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18243,6 +18243,20 @@
         <v>6860</v>
       </c>
     </row>
+    <row r="1278" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1278" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B1278" s="2">
+        <v>0.65464120370370371</v>
+      </c>
+      <c r="C1278">
+        <v>180965</v>
+      </c>
+      <c r="D1278">
+        <v>6860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A79A27-4F72-4748-824A-5D3A95FC4355}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B57920-97FA-4BD3-82D1-24F3A3D4EB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4065" yWindow="4065" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4410" yWindow="4410" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1278"/>
+  <dimension ref="A1:D1279"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18257,6 +18257,20 @@
         <v>6860</v>
       </c>
     </row>
+    <row r="1279" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1279" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B1279" s="2">
+        <v>0.65077546296296296</v>
+      </c>
+      <c r="C1279">
+        <v>181057</v>
+      </c>
+      <c r="D1279">
+        <v>6860</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B57920-97FA-4BD3-82D1-24F3A3D4EB0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C50DE4-990E-4336-A4A6-8A255B79AF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4410" yWindow="4410" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4755" yWindow="4755" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1279"/>
+  <dimension ref="A1:D1280"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18271,6 +18271,20 @@
         <v>6860</v>
       </c>
     </row>
+    <row r="1280" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1280" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B1280" s="2">
+        <v>0.39961805555555557</v>
+      </c>
+      <c r="C1280">
+        <v>181381</v>
+      </c>
+      <c r="D1280">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C50DE4-990E-4336-A4A6-8A255B79AF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308E9700-6895-4F87-96ED-F8613F37837D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4755" yWindow="4755" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5100" yWindow="0" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1280"/>
+  <dimension ref="A1:D1281"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18285,6 +18285,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1281" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1281" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B1281" s="2">
+        <v>0.51143518518518516</v>
+      </c>
+      <c r="C1281">
+        <v>181428</v>
+      </c>
+      <c r="D1281">
+        <v>6850</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{308E9700-6895-4F87-96ED-F8613F37837D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD93FDA-AD99-4253-9EC4-69EAF4F28F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="0" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5445" yWindow="5445" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1281"/>
+  <dimension ref="A1:D1282"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18299,6 +18299,20 @@
         <v>6850</v>
       </c>
     </row>
+    <row r="1282" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1282" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B1282" s="2">
+        <v>0.67915509259259255</v>
+      </c>
+      <c r="C1282">
+        <v>181435</v>
+      </c>
+      <c r="D1282">
+        <v>6840</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AD93FDA-AD99-4253-9EC4-69EAF4F28F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF73D503-BCE6-4483-937B-F9895CB5762A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5445" yWindow="5445" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5790" yWindow="0" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1282"/>
+  <dimension ref="A1:D1283"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18313,6 +18313,20 @@
         <v>6840</v>
       </c>
     </row>
+    <row r="1283" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1283" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B1283" s="2">
+        <v>0.44622685185185185</v>
+      </c>
+      <c r="C1283">
+        <v>181456</v>
+      </c>
+      <c r="D1283">
+        <v>6790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF73D503-BCE6-4483-937B-F9895CB5762A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B168E94-EF1B-46D8-851D-F1D9C79156AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5790" yWindow="0" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6135" yWindow="6135" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1283"/>
+  <dimension ref="A1:D1284"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18327,6 +18327,20 @@
         <v>6790</v>
       </c>
     </row>
+    <row r="1284" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1284" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B1284" s="2">
+        <v>0.64121527777777776</v>
+      </c>
+      <c r="C1284">
+        <v>181433</v>
+      </c>
+      <c r="D1284">
+        <v>6790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B168E94-EF1B-46D8-851D-F1D9C79156AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B120CD5-B64F-4282-9829-58BFF9774FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6135" yWindow="6135" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1284"/>
+  <dimension ref="A1:D1285"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18341,6 +18341,20 @@
         <v>6790</v>
       </c>
     </row>
+    <row r="1285" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1285" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B1285" s="2">
+        <v>0.6346180555555555</v>
+      </c>
+      <c r="C1285">
+        <v>181474</v>
+      </c>
+      <c r="D1285">
+        <v>6790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B120CD5-B64F-4282-9829-58BFF9774FC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE0146C-0202-4021-AD8D-CE3FF7C89A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1285"/>
+  <dimension ref="A1:D1286"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18355,6 +18355,20 @@
         <v>6790</v>
       </c>
     </row>
+    <row r="1286" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1286" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B1286" s="2">
+        <v>0.62864583333333335</v>
+      </c>
+      <c r="C1286">
+        <v>181495</v>
+      </c>
+      <c r="D1286">
+        <v>6790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFE0146C-0202-4021-AD8D-CE3FF7C89A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D304ED-EB46-4E4F-8C0B-B2B9ACE04974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2250" yWindow="2250" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1286"/>
+  <dimension ref="A1:D1287"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18369,6 +18369,20 @@
         <v>6790</v>
       </c>
     </row>
+    <row r="1287" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1287" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B1287" s="2">
+        <v>0.36785879629629631</v>
+      </c>
+      <c r="C1287">
+        <v>181613</v>
+      </c>
+      <c r="D1287">
+        <v>6790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2D304ED-EB46-4E4F-8C0B-B2B9ACE04974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E81239E-01A7-4E21-AEFA-CC63343F8AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2595" yWindow="2595" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1287"/>
+  <dimension ref="A1:D1288"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18383,6 +18383,20 @@
         <v>6790</v>
       </c>
     </row>
+    <row r="1288" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1288" s="1">
+        <v>46320</v>
+      </c>
+      <c r="B1288" s="2">
+        <v>0.39637731481481481</v>
+      </c>
+      <c r="C1288">
+        <v>181615</v>
+      </c>
+      <c r="D1288">
+        <v>6790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E81239E-01A7-4E21-AEFA-CC63343F8AF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E440EBF0-6CBF-4D3D-87F7-FA01D30EF22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="2595" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1288"/>
+  <dimension ref="A1:D1289"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18397,6 +18397,20 @@
         <v>6790</v>
       </c>
     </row>
+    <row r="1289" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1289" s="1">
+        <v>46321</v>
+      </c>
+      <c r="B1289" s="2">
+        <v>0.64090277777777782</v>
+      </c>
+      <c r="C1289">
+        <v>181622</v>
+      </c>
+      <c r="D1289">
+        <v>6790</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E440EBF0-6CBF-4D3D-87F7-FA01D30EF22A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CCA1DA-393E-4D54-BCEF-8BA59408E58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2940" yWindow="2940" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3285" yWindow="3285" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1289"/>
+  <dimension ref="A1:D1290"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18411,6 +18411,20 @@
         <v>6790</v>
       </c>
     </row>
+    <row r="1290" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1290" s="1">
+        <v>46322</v>
+      </c>
+      <c r="B1290" s="2">
+        <v>0.62959490740740742</v>
+      </c>
+      <c r="C1290">
+        <v>181729</v>
+      </c>
+      <c r="D1290">
+        <v>6800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65CCA1DA-393E-4D54-BCEF-8BA59408E58C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC63C39C-B9E3-46D8-AD9A-FDB40D3CD003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="3285" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3630" yWindow="3630" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1290"/>
+  <dimension ref="A1:D1291"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18425,6 +18425,20 @@
         <v>6800</v>
       </c>
     </row>
+    <row r="1291" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1291" s="1">
+        <v>46323</v>
+      </c>
+      <c r="B1291" s="2">
+        <v>0.64189814814814816</v>
+      </c>
+      <c r="C1291">
+        <v>181749</v>
+      </c>
+      <c r="D1291">
+        <v>6800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC63C39C-B9E3-46D8-AD9A-FDB40D3CD003}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F5CD41-A0CC-4ED8-AFFA-E60BEF0D39B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3630" yWindow="3630" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3975" yWindow="3975" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1291"/>
+  <dimension ref="A1:D1292"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18439,6 +18439,20 @@
         <v>6800</v>
       </c>
     </row>
+    <row r="1292" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1292" s="1">
+        <v>46324</v>
+      </c>
+      <c r="B1292" s="2">
+        <v>0.63745370370370369</v>
+      </c>
+      <c r="C1292">
+        <v>181780</v>
+      </c>
+      <c r="D1292">
+        <v>6800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F5CD41-A0CC-4ED8-AFFA-E60BEF0D39B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FA7F5B-E2D0-4954-962F-07815A6EC04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3975" yWindow="3975" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4320" yWindow="4320" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1292"/>
+  <dimension ref="A1:D1293"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18453,6 +18453,20 @@
         <v>6800</v>
       </c>
     </row>
+    <row r="1293" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1293" s="1">
+        <v>46325</v>
+      </c>
+      <c r="B1293" s="2">
+        <v>0.64277777777777778</v>
+      </c>
+      <c r="C1293">
+        <v>181839</v>
+      </c>
+      <c r="D1293">
+        <v>6800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/disk_savvy.xlsx
+++ b/disk_savvy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acer\Desktop\NAUKA\Python Nauka\data_science\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FA7F5B-E2D0-4954-962F-07815A6EC04C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A173A76-CCBD-4223-857A-D05198A40E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4320" yWindow="4320" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4665" yWindow="4665" windowWidth="5085" windowHeight="9375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arkusz1" sheetId="1" r:id="rId1"/>
@@ -356,7 +356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D1293"/>
+  <dimension ref="A1:D1294"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -18467,6 +18467,20 @@
         <v>6800</v>
       </c>
     </row>
+    <row r="1294" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1294" s="1">
+        <v>46326</v>
+      </c>
+      <c r="B1294" s="2">
+        <v>0.40203703703703703</v>
+      </c>
+      <c r="C1294">
+        <v>181849</v>
+      </c>
+      <c r="D1294">
+        <v>6800</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
